--- a/data/trans_orig/IP07A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A02-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>32936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30700</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>43807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60245</t>
+          <t>60040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23122</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>44756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93411</t>
+          <t>93400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116665</t>
+          <t>116223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118280</t>
+          <t>117554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141856</t>
+          <t>141385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218764</t>
+          <t>218127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>251752</t>
+          <t>251384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72249</t>
+          <t>73205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95535</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>80386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103521</t>
+          <t>103708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158577</t>
+          <t>159631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192679</t>
+          <t>194487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39918</t>
+          <t>40369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>51146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>68905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43253</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>30531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50913</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69854</t>
+          <t>68943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145782</t>
+          <t>145351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>174280</t>
+          <t>175179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174714</t>
+          <t>172278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203520</t>
+          <t>204023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>328176</t>
+          <t>327218</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122861</t>
+          <t>122966</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151491</t>
+          <t>152239</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>120362</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>254883</t>
+          <t>250931</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295138</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>23953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28025</t>
+          <t>28258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43952</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>23966</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45903</t>
+          <t>47178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>63475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>90410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98614</t>
+          <t>97775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122737</t>
+          <t>123467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171946</t>
+          <t>173400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206799</t>
+          <t>208836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>98169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121788</t>
+          <t>121284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83974</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108935</t>
+          <t>108717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189369</t>
+          <t>188314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223671</t>
+          <t>222890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37792</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29167</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56982</t>
+          <t>57102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37836</t>
+          <t>37729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>52290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70766</t>
+          <t>70824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>137516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165157</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>253635</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>294191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157650</t>
+          <t>157122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187118</t>
+          <t>185586</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136557</t>
+          <t>133764</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>166568</t>
+          <t>164726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>298700</t>
+          <t>301737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>343914</t>
+          <t>342502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34892</t>
+          <t>35741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48942</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>27472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130765</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156249</t>
+          <t>156792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143807</t>
+          <t>143406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169235</t>
+          <t>167819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280420</t>
+          <t>281998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319082</t>
+          <t>319497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78907</t>
+          <t>79305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104359</t>
+          <t>104308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>67071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90643</t>
+          <t>90212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151659</t>
+          <t>151170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189192</t>
+          <t>187851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26831</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43016</t>
+          <t>43709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48596</t>
+          <t>49250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81856</t>
+          <t>79852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101765</t>
+          <t>101542</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>25919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40053</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>22046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39273</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14553</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181633</t>
+          <t>183699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>213641</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222138</t>
+          <t>219998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251939</t>
+          <t>252274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>413795</t>
+          <t>414250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>458273</t>
+          <t>457316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118909</t>
+          <t>120662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149764</t>
+          <t>149727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119371</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215620</t>
+          <t>217282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259512</t>
+          <t>260519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
